--- a/data/forgotten.xlsx
+++ b/data/forgotten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tchakra2/cnc-fun/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9273712-372E-AF46-86AB-CF22C268727D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0E8B25-38DF-AF48-B9ED-4147D3C12E1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" activeTab="1" xr2:uid="{91B247F1-4191-D447-A616-0E249F0596B9}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{91B247F1-4191-D447-A616-0E249F0596B9}"/>
   </bookViews>
   <sheets>
     <sheet name="forgotten" sheetId="1" r:id="rId1"/>
@@ -8577,6 +8577,9 @@
       <c r="E79" s="5">
         <v>9</v>
       </c>
+      <c r="F79" s="5">
+        <v>3</v>
+      </c>
       <c r="G79" s="5">
         <v>34</v>
       </c>
@@ -43702,7 +43705,9 @@
       <c r="C839" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E839" s="11"/>
+      <c r="E839" s="11">
+        <v>0</v>
+      </c>
       <c r="F839" s="5">
         <v>2</v>
       </c>
@@ -43723,7 +43728,9 @@
       <c r="C840" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E840" s="11"/>
+      <c r="E840" s="11">
+        <v>0</v>
+      </c>
       <c r="F840" s="5">
         <v>2</v>
       </c>

--- a/data/forgotten.xlsx
+++ b/data/forgotten.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tchakra2/cnc-fun/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D3ADF87-C0E3-3346-AF63-32B8552D7F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961D0785-7ADD-DD4D-8254-2C4EB5812BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{91B247F1-4191-D447-A616-0E249F0596B9}"/>
   </bookViews>
@@ -4236,7 +4236,8 @@
   <cols>
     <col min="1" max="1" width="28.33203125" style="3" customWidth="1"/>
     <col min="2" max="2" width="45.33203125" style="3" customWidth="1"/>
-    <col min="3" max="4" width="10.83203125" style="3"/>
+    <col min="3" max="3" width="10.83203125" style="3"/>
+    <col min="4" max="4" width="38" style="3" customWidth="1"/>
     <col min="5" max="5" width="13.1640625" style="3" customWidth="1"/>
     <col min="6" max="6" width="13.83203125" style="3" customWidth="1"/>
     <col min="7" max="9" width="10.83203125" style="3"/>

--- a/data/forgotten.xlsx
+++ b/data/forgotten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tchakra2/cnc-fun/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961D0785-7ADD-DD4D-8254-2C4EB5812BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9072D9-57FF-2D4C-9A65-94D5398D10E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="34560" windowHeight="21600" xr2:uid="{91B247F1-4191-D447-A616-0E249F0596B9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7626" uniqueCount="1256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7631" uniqueCount="1258">
   <si>
     <t>Attack: New York</t>
   </si>
@@ -3807,6 +3807,12 @@
   </si>
   <si>
     <t>6/26/2026, 01:19:32</t>
+  </si>
+  <si>
+    <t>London, New York</t>
+  </si>
+  <si>
+    <t>Boston, New York</t>
   </si>
 </sst>
 </file>
@@ -45620,6 +45626,9 @@
       <c r="C875" s="3" t="s">
         <v>65</v>
       </c>
+      <c r="D875" s="3" t="s">
+        <v>63</v>
+      </c>
       <c r="E875" s="3">
         <v>3</v>
       </c>
@@ -45712,6 +45721,9 @@
       <c r="C879" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="D879" s="3" t="s">
+        <v>1257</v>
+      </c>
       <c r="E879" s="3">
         <v>35</v>
       </c>
@@ -46080,7 +46092,9 @@
       <c r="C895" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D895" s="4"/>
+      <c r="D895" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="E895" s="3">
         <v>40</v>
       </c>
@@ -46173,6 +46187,9 @@
       <c r="C899" s="3" t="s">
         <v>64</v>
       </c>
+      <c r="D899" s="3" t="s">
+        <v>60</v>
+      </c>
       <c r="E899" s="3">
         <v>40</v>
       </c>
@@ -46196,7 +46213,9 @@
       <c r="C900" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D900" s="4"/>
+      <c r="D900" s="4" t="s">
+        <v>1256</v>
+      </c>
       <c r="E900" s="3">
         <v>1</v>
       </c>
@@ -47164,5 +47183,6 @@
   </sheetData>
   <dataConsolidate/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>